--- a/healthcare_forms/010_patient_encounter_form_template--healthcare_forms.xlsx
+++ b/healthcare_forms/010_patient_encounter_form_template--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>allergies</t>
+          <t>allergies_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Allergies</t>
+          <t>Allergies 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,7 +957,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>medications</t>
+          <t>medications_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>lab_results</t>
+          <t>lab_results_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lab Results</t>
+          <t>Lab Results 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Radiology Results</t>
+          <t>Radiology Results (2)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'dr._smith'}</t>
+          <t>dr._smith</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Dr. Smith'}</t>
+          <t>Dr. Smith</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'dr._lee'}</t>
+          <t>dr._lee</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Dr. Lee'}</t>
+          <t>Dr. Lee</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'dr._johnson'}</t>
+          <t>dr._johnson</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Dr. Johnson'}</t>
+          <t>Dr. Johnson</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'penicillin'}</t>
+          <t>penicillin</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Penicillin'}</t>
+          <t>Penicillin</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'polysaccharide'}</t>
+          <t>polysaccharide</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Polysaccharide'}</t>
+          <t>Polysaccharide</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'atenolol'}</t>
+          <t>atenolol</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Atenolol'}</t>
+          <t>Atenolol</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'metoprolol'}</t>
+          <t>metoprolol</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Metoprolol'}</t>
+          <t>Metoprolol</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'cbc'}</t>
+          <t>cbc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'CBC'}</t>
+          <t>CBC</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'chem_12'}</t>
+          <t>chem_12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Chem 12'}</t>
+          <t>Chem 12</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'influenza'}</t>
+          <t>influenza</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Influenza'}</t>
+          <t>Influenza</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'pneumonia'}</t>
+          <t>pneumonia</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Pneumonia'}</t>
+          <t>Pneumonia</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'bronchitis'}</t>
+          <t>bronchitis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Bronchitis'}</t>
+          <t>Bronchitis</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'antivirus'}</t>
+          <t>antivirus</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Antivirus'}</t>
+          <t>Antivirus</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'antibiotik'}</t>
+          <t>antibiotik</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Antibiotik'}</t>
+          <t>Antibiotik</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'rest'}</t>
+          <t>rest</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Rest'}</t>
+          <t>Rest</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'ecg'}</t>
+          <t>ecg</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'ECG'}</t>
+          <t>ECG</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'ultrasound'}</t>
+          <t>ultrasound</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Ultrasound'}</t>
+          <t>Ultrasound</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'mri'}</t>
+          <t>mri</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'MRI'}</t>
+          <t>MRI</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'ct'}</t>
+          <t>ct</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'CT'}</t>
+          <t>CT</t>
         </is>
       </c>
     </row>
